--- a/Dashboards/Data final/variacion_empleo_significancia.xlsx
+++ b/Dashboards/Data final/variacion_empleo_significancia.xlsx
@@ -424,25 +424,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>44.40936647134281</v>
+        <v>44.76819748375117</v>
       </c>
       <c r="E2">
-        <v>0.3485973519574447</v>
+        <v>0.3486500674633998</v>
       </c>
       <c r="F2">
-        <v>42.81845568746375</v>
+        <v>43.19946500861845</v>
       </c>
       <c r="G2">
-        <v>0.3494354338469753</v>
+        <v>0.349546607880466</v>
       </c>
       <c r="H2">
-        <v>1.59091078387906</v>
+        <v>1.56873247513272</v>
       </c>
       <c r="I2">
-        <v>3.223180961142278</v>
+        <v>3.177501399529012</v>
       </c>
       <c r="J2">
-        <v>0.001267754353545092</v>
+        <v>0.001485499729839246</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -463,22 +463,22 @@
         </is>
       </c>
       <c r="D3">
-        <v>38.82025419437831</v>
+        <v>39.17685803826048</v>
       </c>
       <c r="E3">
-        <v>0.3438688042300586</v>
+        <v>0.3443488311726653</v>
       </c>
       <c r="F3">
-        <v>44.40936647134281</v>
+        <v>44.76819748375117</v>
       </c>
       <c r="G3">
-        <v>0.3485973519574447</v>
+        <v>0.3486500674633998</v>
       </c>
       <c r="H3">
-        <v>-5.589112276964492</v>
+        <v>-5.591339445490689</v>
       </c>
       <c r="I3">
-        <v>-11.41429662099499</v>
+        <v>-11.41011304307557</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -502,22 +502,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>44.43810156568256</v>
+        <v>44.67555035694984</v>
       </c>
       <c r="E4">
-        <v>0.3471846556532963</v>
+        <v>0.3471799128338692</v>
       </c>
       <c r="F4">
-        <v>38.82025419437831</v>
+        <v>39.17685803826048</v>
       </c>
       <c r="G4">
-        <v>0.3438688042300586</v>
+        <v>0.3443488311726653</v>
       </c>
       <c r="H4">
-        <v>5.617847371304244</v>
+        <v>5.498692318689365</v>
       </c>
       <c r="I4">
-        <v>11.496570017529</v>
+        <v>11.24502799554051</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -541,25 +541,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>45.28735869703763</v>
+        <v>45.52861340384431</v>
       </c>
       <c r="E5">
-        <v>0.4208095232689079</v>
+        <v>0.4208394146189235</v>
       </c>
       <c r="F5">
-        <v>44.43810156568256</v>
+        <v>44.67555035694984</v>
       </c>
       <c r="G5">
-        <v>0.3471846556532963</v>
+        <v>0.3471799128338692</v>
       </c>
       <c r="H5">
-        <v>0.8492571313550741</v>
+        <v>0.8530630468944693</v>
       </c>
       <c r="I5">
-        <v>1.556717193850648</v>
+        <v>1.563636130471856</v>
       </c>
       <c r="J5">
-        <v>0.1195376446165177</v>
+        <v>0.1179030448393643</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>46.29894806082012</v>
+        <v>46.53187169487655</v>
       </c>
       <c r="E6">
-        <v>0.3914836396628411</v>
+        <v>0.3913244224505995</v>
       </c>
       <c r="F6">
-        <v>45.28735869703763</v>
+        <v>45.52861340384431</v>
       </c>
       <c r="G6">
-        <v>0.4208095232689079</v>
+        <v>0.4208394146189235</v>
       </c>
       <c r="H6">
-        <v>1.011589363782491</v>
+        <v>1.003258291032239</v>
       </c>
       <c r="I6">
-        <v>1.760044343078104</v>
+        <v>1.745812160646057</v>
       </c>
       <c r="J6">
-        <v>0.07840028837872426</v>
+        <v>0.0808435971667476</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -619,25 +619,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>47.57195338854709</v>
+        <v>47.8640444632001</v>
       </c>
       <c r="E7">
-        <v>0.3627610644663421</v>
+        <v>0.3625953116224431</v>
       </c>
       <c r="F7">
-        <v>46.29894806082012</v>
+        <v>46.53187169487655</v>
       </c>
       <c r="G7">
-        <v>0.3914836396628411</v>
+        <v>0.3913244224505995</v>
       </c>
       <c r="H7">
-        <v>1.273005327726963</v>
+        <v>1.332172768323552</v>
       </c>
       <c r="I7">
-        <v>2.385164159878892</v>
+        <v>2.497096634202475</v>
       </c>
       <c r="J7">
-        <v>0.01707150162125459</v>
+        <v>0.01252148292787481</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -658,25 +658,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>48.91312461089052</v>
+        <v>49.28423584153995</v>
       </c>
       <c r="E8">
-        <v>0.3474288523713501</v>
+        <v>0.3472474635416927</v>
       </c>
       <c r="F8">
-        <v>47.57195338854709</v>
+        <v>47.8640444632001</v>
       </c>
       <c r="G8">
-        <v>0.3627610644663421</v>
+        <v>0.3625953116224431</v>
       </c>
       <c r="H8">
-        <v>1.341171222343434</v>
+        <v>1.420191378339851</v>
       </c>
       <c r="I8">
-        <v>2.670075473991494</v>
+        <v>2.828773749565128</v>
       </c>
       <c r="J8">
-        <v>0.007583419898436361</v>
+        <v>0.004672671969633058</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -697,25 +697,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>46.17194224985008</v>
+        <v>46.50281943043307</v>
       </c>
       <c r="E9">
-        <v>0.3290558996199425</v>
+        <v>0.3290110064160756</v>
       </c>
       <c r="F9">
-        <v>48.91312461089052</v>
+        <v>49.28423584153995</v>
       </c>
       <c r="G9">
-        <v>0.3474288523713501</v>
+        <v>0.3472474635416927</v>
       </c>
       <c r="H9">
-        <v>-2.741182361040444</v>
+        <v>-2.781416411106882</v>
       </c>
       <c r="I9">
-        <v>-5.728419281411955</v>
+        <v>-5.814474100300274</v>
       </c>
       <c r="J9">
-        <v>1.01370767335851E-08</v>
+        <v>6.082480075164653E-09</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="D10">
-        <v>40.74096087322953</v>
+        <v>41.18860875336681</v>
       </c>
       <c r="E10">
-        <v>0.3370115714707861</v>
+        <v>0.3374008982911252</v>
       </c>
       <c r="F10">
-        <v>46.17194224985008</v>
+        <v>46.50281943043307</v>
       </c>
       <c r="G10">
-        <v>0.3290558996199425</v>
+        <v>0.3290110064160756</v>
       </c>
       <c r="H10">
-        <v>-5.430981376620544</v>
+        <v>-5.314210677066256</v>
       </c>
       <c r="I10">
-        <v>-11.53039299754209</v>
+        <v>-11.27655919046325</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -775,25 +775,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>41.88428098021372</v>
+        <v>42.2642911281628</v>
       </c>
       <c r="E11">
-        <v>0.3403264810027898</v>
+        <v>0.3406014146242619</v>
       </c>
       <c r="F11">
-        <v>40.74096087322953</v>
+        <v>41.18860875336681</v>
       </c>
       <c r="G11">
-        <v>0.3370115714707861</v>
+        <v>0.3374008982911252</v>
       </c>
       <c r="H11">
-        <v>1.143320106984184</v>
+        <v>1.075682374795988</v>
       </c>
       <c r="I11">
-        <v>2.387108523302106</v>
+        <v>2.243690951256577</v>
       </c>
       <c r="J11">
-        <v>0.01698147765018998</v>
+        <v>0.0248522927225161</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -814,25 +814,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>40.30517701938917</v>
+        <v>40.63761586806899</v>
       </c>
       <c r="E12">
-        <v>0.5614163447099995</v>
+        <v>0.5669811371404357</v>
       </c>
       <c r="F12">
-        <v>41.88428098021372</v>
+        <v>42.2642911281628</v>
       </c>
       <c r="G12">
-        <v>0.3403264810027898</v>
+        <v>0.3406014146242619</v>
       </c>
       <c r="H12">
-        <v>-1.579103960824547</v>
+        <v>-1.626675260093812</v>
       </c>
       <c r="I12">
-        <v>-2.405286618338103</v>
+        <v>-2.459366663681819</v>
       </c>
       <c r="J12">
-        <v>0.01615978607527935</v>
+        <v>0.01391823875127196</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -853,25 +853,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>38.5578817960552</v>
+        <v>38.84821771526936</v>
       </c>
       <c r="E13">
-        <v>0.6536392677344107</v>
+        <v>0.658419127370682</v>
       </c>
       <c r="F13">
-        <v>40.30517701938917</v>
+        <v>40.63761586806899</v>
       </c>
       <c r="G13">
-        <v>0.5614163447099995</v>
+        <v>0.5669811371404357</v>
       </c>
       <c r="H13">
-        <v>-1.747295223333971</v>
+        <v>-1.789398152799627</v>
       </c>
       <c r="I13">
-        <v>-2.027859079830116</v>
+        <v>-2.059388558674145</v>
       </c>
       <c r="J13">
-        <v>0.04257463253130767</v>
+        <v>0.03945703091441932</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -892,25 +892,25 @@
         </is>
       </c>
       <c r="D14">
-        <v>30.57369110974986</v>
+        <v>30.8482223146526</v>
       </c>
       <c r="E14">
-        <v>0.7395787271557988</v>
+        <v>0.7454694263853667</v>
       </c>
       <c r="F14">
-        <v>38.5578817960552</v>
+        <v>38.84821771526936</v>
       </c>
       <c r="G14">
-        <v>0.6536392677344107</v>
+        <v>0.658419127370682</v>
       </c>
       <c r="H14">
-        <v>-7.984190686305336</v>
+        <v>-7.999995400616761</v>
       </c>
       <c r="I14">
-        <v>-8.089136432510864</v>
+        <v>-8.043384173622917</v>
       </c>
       <c r="J14">
-        <v>6.661338147750939E-16</v>
+        <v>8.881784197001252E-16</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -931,25 +931,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>33.60712943950971</v>
+        <v>33.9412318290706</v>
       </c>
       <c r="E15">
-        <v>1.082445648632445</v>
+        <v>1.08995499591888</v>
       </c>
       <c r="F15">
-        <v>30.57369110974986</v>
+        <v>30.8482223146526</v>
       </c>
       <c r="G15">
-        <v>0.7395787271557988</v>
+        <v>0.7454694263853667</v>
       </c>
       <c r="H15">
-        <v>3.033438329759843</v>
+        <v>3.093009514417993</v>
       </c>
       <c r="I15">
-        <v>2.313873002120502</v>
+        <v>2.342297553318962</v>
       </c>
       <c r="J15">
-        <v>0.02067468944136985</v>
+        <v>0.01916542840014479</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -970,25 +970,25 @@
         </is>
       </c>
       <c r="D16">
-        <v>35.8529999005698</v>
+        <v>36.03571922987221</v>
       </c>
       <c r="E16">
-        <v>1.19238412062456</v>
+        <v>1.197949396193277</v>
       </c>
       <c r="F16">
-        <v>33.60712943950971</v>
+        <v>33.9412318290706</v>
       </c>
       <c r="G16">
-        <v>1.082445648632445</v>
+        <v>1.08995499591888</v>
       </c>
       <c r="H16">
-        <v>2.245870461060093</v>
+        <v>2.094487400801619</v>
       </c>
       <c r="I16">
-        <v>1.394582517535751</v>
+        <v>1.293217578659289</v>
       </c>
       <c r="J16">
-        <v>0.1631417700251983</v>
+        <v>0.19593581752653</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1009,25 +1009,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>35.74721286783235</v>
+        <v>35.91641035696664</v>
       </c>
       <c r="E17">
-        <v>1.160962037586491</v>
+        <v>1.171500490455538</v>
       </c>
       <c r="F17">
-        <v>35.8529999005698</v>
+        <v>36.03571922987221</v>
       </c>
       <c r="G17">
-        <v>1.19238412062456</v>
+        <v>1.197949396193277</v>
       </c>
       <c r="H17">
-        <v>-0.105787032737453</v>
+        <v>-0.1193088729055702</v>
       </c>
       <c r="I17">
-        <v>-0.06356571130995442</v>
+        <v>-0.07120543729697887</v>
       </c>
       <c r="J17">
-        <v>0.9493160349141181</v>
+        <v>0.943234254066504</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>32.87280611429867</v>
+        <v>33.02956536674087</v>
       </c>
       <c r="E18">
-        <v>1.712301383252417</v>
+        <v>1.721187650190498</v>
       </c>
       <c r="F18">
-        <v>35.74721286783235</v>
+        <v>35.91641035696664</v>
       </c>
       <c r="G18">
-        <v>1.160962037586491</v>
+        <v>1.171500490455538</v>
       </c>
       <c r="H18">
-        <v>-2.874406753533677</v>
+        <v>-2.886844990225775</v>
       </c>
       <c r="I18">
-        <v>-1.389427968779199</v>
+        <v>-1.386544801637147</v>
       </c>
       <c r="J18">
-        <v>0.1647026503384428</v>
+        <v>0.1655806099012096</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
